--- a/documentation/Lab8_Project_Tracker.xlsx
+++ b/documentation/Lab8_Project_Tracker.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="21942" windowHeight="9737" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
@@ -29,75 +28,239 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Gap Analysis'!$A$4:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Risks &amp; Issues'!$A$4:$K$26</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd mmm yyyy"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="dd\ mmm\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="001F3A5F"/>
+      <color rgb="FF1F3A5F"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="134"/>
       <i val="1"/>
-      <color rgb="00595959"/>
+      <color rgb="FF595959"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="134"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="134"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000000FF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F3A5F"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="000563C1"/>
+      <charset val="134"/>
+      <color rgb="FF0563C1"/>
       <sz val="10"/>
       <u val="single"/>
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="007F7F7F"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FF1F3A5F"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <color rgb="FF0000FF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill/>
     </fill>
@@ -106,21 +269,210 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3A5F"/>
+        <fgColor rgb="FF1F3A5F"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7ECF3"/>
+        <fgColor rgb="FFE7ECF3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -130,23 +482,146 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -154,105 +629,285 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="8">
     <dxf>
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="00595959"/>
+        <color rgb="FF595959"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00F2F2F2"/>
+          <fgColor rgb="FFF2F2F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -260,11 +915,11 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="001F4E78"/>
+        <color rgb="FF1F4E78"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00DDEBF7"/>
+          <fgColor rgb="FFDDEBF7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -272,11 +927,11 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="009C0006"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFC7CE"/>
+          <fgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -284,11 +939,11 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="00C65911"/>
+        <color rgb="FFC65911"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FCE4D6"/>
+          <fgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -296,11 +951,11 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="009C5700"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFEB9C"/>
+          <fgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -308,11 +963,11 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="00006100"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00C6EFCE"/>
+          <fgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -320,11 +975,11 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="007F7F7F"/>
+        <color rgb="FF7F7F7F"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00EDEDED"/>
+          <fgColor rgb="FFEDEDED"/>
         </patternFill>
       </fill>
     </dxf>
@@ -332,7 +987,7 @@
       <font>
         <name val="Arial"/>
         <i val="1"/>
-        <color rgb="007F7F7F"/>
+        <color rgb="FF7F7F7F"/>
       </font>
     </dxf>
   </dxfs>
@@ -687,26 +1342,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F3A5F"/>
+    <tabColor rgb="FF1F3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C75"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C76"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.55"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="96" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Lab 8 — Product Lifecycle &amp; Portfolio Intelligence</t>
@@ -720,8 +1374,8 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="15.4" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Project at a glance</t>
         </is>
@@ -751,7 +1405,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="24.85" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Opening problem</t>
@@ -829,7 +1483,7 @@
           <t>Current team</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Guna</t>
         </is>
@@ -841,7 +1495,7 @@
           <t>Programme owner</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
+      <c r="B14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -849,7 +1503,7 @@
           <t>Live demo</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>ilp-ppl-dash-board.vercel.app</t>
         </is>
@@ -861,19 +1515,19 @@
           <t>Tracker as of</t>
         </is>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="20">
         <f>TODAY()</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="18" ht="15.4" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Scope (team's problem understanding)</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="24.85" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>In scope</t>
@@ -885,7 +1539,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="24.85" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Out of scope</t>
@@ -897,8 +1551,8 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="22" ht="15.4" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Gates — earliest dates at planned durations</t>
         </is>
@@ -914,7 +1568,7 @@
         <f>'Project Plan'!$O$14</f>
         <v/>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="20">
         <f>'Project Plan'!$L$14</f>
         <v/>
       </c>
@@ -929,12 +1583,12 @@
         <f>'Project Plan'!$O$23</f>
         <v/>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="20">
         <f>'Project Plan'!$L$23</f>
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="24.85" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Gate 3 — Functional prototype — five tabs without AI</t>
@@ -944,7 +1598,7 @@
         <f>'Project Plan'!$O$37</f>
         <v/>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="20">
         <f>'Project Plan'!$L$37</f>
         <v/>
       </c>
@@ -959,7 +1613,7 @@
         <f>'Project Plan'!$O$45</f>
         <v/>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="20">
         <f>'Project Plan'!$L$45</f>
         <v/>
       </c>
@@ -975,8 +1629,8 @@
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="29" ht="15.4" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1048,7 +1702,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="24.85" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Tab-rework activities still needing an estimate (3.2–3.6)</t>
@@ -1125,14 +1779,14 @@
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="44" ht="15.4" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>Headlines</t>
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="24.85" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
           <t>•</t>
@@ -1144,7 +1798,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="24.85" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>•</t>
@@ -1168,7 +1822,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="24.85" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>•</t>
@@ -1180,22 +1834,23 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>TODO.md (the dev-level tracker, separate from this Project Plan) stood at 30 Sep 2026: 12 of 17 tracked phases Done, 2 partly done, 2 open, 1 decided (~71%). By checkbox count 19/53 (~36%) — lower because most completed phases (schema, dataset generation, the database, branding) were logged as narrative/tables rather than checkboxes, while nearly all remaining open work is checkbox-tracked, so the checkbox ratio understates progress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15.4" customHeight="1"/>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>What this tracker replaces</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>The 16-phase plan (screenshot) — including a 'Core CRM Modules' row that does not apply to this product.</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1862,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>The team tracker's Project Tracker, Project Internal Tracker and Action Plan tabs — their content is merged here.</t>
+          <t>The 16-phase plan (screenshot) — including a 'Core CRM Modules' row that does not apply to this product.</t>
         </is>
       </c>
     </row>
@@ -1219,235 +1874,249 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
+          <t>The team tracker's Project Tracker, Project Internal Tracker and Action Plan tabs — their content is merged here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
           <t>The first version of this tracker.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="55" ht="15.4" customHeight="1"/>
+    <row r="56" ht="24.85" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>Tabs</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>Project Plan</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>P0–P4 with Gates 1–4. Owner, status, dates, dependencies, definition of done. Source column shows where each row came from.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Open Questions</t>
+          <t>Project Plan</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>The 15 decisions we need, each with a recommendation and a default.</t>
+          <t>P0–P4 with Gates 1–4. Owner, status, dates, dependencies, definition of done. Source column shows where each row came from.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Stakeholder Meetings</t>
+          <t>Open Questions</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Meetings M1–M8 and the questions each settles.</t>
+          <t>The 15 decisions we need, each with a recommendation and a default.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Gap Analysis</t>
+          <t>Stakeholder Meetings</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>The team's 44 functional gaps, each mapped to a plan step.</t>
+          <t>Meetings M1–M8 and the questions each settles.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Personas &amp; Journey</t>
+          <t>Gap Analysis</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Who needs what; current → future journey; the end-to-end decision journey.</t>
+          <t>The team's 44 functional gaps, each mapped to a plan step.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Risks &amp; Issues</t>
+          <t>Personas &amp; Journey</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>What could go wrong or already has, with severity.</t>
+          <t>Who needs what; current → future journey; the end-to-end decision journey.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Decisions</t>
+          <t>Risks &amp; Issues</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Decisions made, why, and when to revisit.</t>
+          <t>What could go wrong or already has, with severity.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Architecture Roadmap</t>
+          <t>Decisions</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>How we get from today's architecture to the target.</t>
+          <t>Decisions made, why, and when to revisit.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Research &amp; Data</t>
+          <t>Architecture Roadmap</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Our research and the team's; the dataset we built and its gaps.</t>
+          <t>How we get from today's architecture to the target.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Handover Findings</t>
+          <t>Research &amp; Data</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>The condition of what we received — the reverse-KT agenda.</t>
+          <t>Our research and the team's; the dataset we built and its gaps.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Timeline</t>
+          <t>Handover Findings</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>What happened and when.</t>
+          <t>The condition of what we received — the reverse-KT agenda.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Benchmark</t>
+          <t>Timeline</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>The team's PLM vendor comparison, with caveats.</t>
+          <t>What happened and when.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
+          <t>Benchmark</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>The team's PLM vendor comparison, with caveats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
           <t>Links</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>Every document, repository and the live demo.</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>Legend</t>
-        </is>
-      </c>
-    </row>
+    <row r="70" ht="15.4" customHeight="1"/>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Light-yellow cell</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>Please fill in or confirm — including role names to replace with people</t>
+          <t>Legend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
+          <t>Light-yellow cell</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Please fill in or confirm — including role names to replace with people</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
           <t>Blue text</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>Typed input — dates and durations you can change</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>Black text</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>Formula or fixed text — do not overwrite formulas</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="11" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="19" t="inlineStr">
         <is>
           <t>Grey italic date</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Tentative — computed from durations; moves when an input changes</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="12" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="16" t="inlineStr">
         <is>
           <t>Shaded row</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>A gate — its date is the latest end of the activities before it</t>
         </is>
@@ -1455,7 +2124,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" display="ilp-ppl-dash-board.vercel.app" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1464,22 +2133,21 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007F7F7F"/>
+    <tabColor rgb="FF7F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.55"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="3" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Architecture Roadmap — from today to the target</t>
@@ -1493,36 +2161,36 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="15.4" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Sequence</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Change</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Why in this order</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Plan step</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr"/>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1556,7 +2224,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="24.85" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2</t>
@@ -1640,7 +2308,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="24.85" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>5</t>
@@ -1724,7 +2392,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="24.85" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>8</t>
@@ -1808,7 +2476,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="24.85" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>11</t>
@@ -1836,7 +2504,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="24.85" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>12</t>
@@ -1864,42 +2532,42 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="19" ht="15.4" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Component view — Now → Next → Future</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr"/>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Now</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Next (trustworthy demo)</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Future (target)</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Plan step</t>
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="24.85" customHeight="1">
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
@@ -2150,12 +2818,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007F7F7F"/>
+    <tabColor rgb="FF7F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.55"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -2165,7 +2833,7 @@
     <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Research &amp; Data — what we learned</t>
@@ -2180,38 +2848,38 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Question it answered</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>What we found</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>What it changed</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="24.85" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>R1</t>
@@ -2293,13 +2961,13 @@
           <t>Metric integrity (3.1c); Q2–Q5.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Report 1 (Google Doc)</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="24.85" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>R4</t>
@@ -2325,13 +2993,13 @@
           <t>Consolidation (3.7); Q7.</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Report 2 (Google Doc)</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="24.85" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>R5</t>
@@ -2357,13 +3025,13 @@
           <t>Q1.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Report 3 (Google Doc)</t>
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="24.85" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>R6</t>
@@ -2395,7 +3063,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="37.3" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>R7</t>
@@ -2427,7 +3095,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="37.3" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>R8</t>
@@ -2459,7 +3127,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="24.85" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>R9</t>
@@ -2491,7 +3159,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="24.85" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>R10</t>
@@ -2523,7 +3191,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="24.85" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>R11</t>
@@ -2551,7 +3219,7 @@
       </c>
       <c r="F15" s="5" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="24.85" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>R12</t>
@@ -2567,11 +3235,11 @@
           <t>What else did we look at, and why did it fall short?</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
       <c r="F16" s="5" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="24.85" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>R13</t>
@@ -2599,7 +3267,7 @@
       </c>
       <c r="F17" s="5" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="24.85" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>R14</t>
@@ -2627,7 +3295,7 @@
       </c>
       <c r="F18" s="5" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="24.85" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>R15</t>
@@ -2657,9 +3325,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" display="Report 1 (Google Doc)" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" display="Report 2 (Google Doc)" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" display="Report 3 (Google Doc)" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2668,12 +3336,12 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007F7F7F"/>
+    <tabColor rgb="FF7F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.55"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -2684,7 +3352,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Handover Findings — the condition of what we received</t>
@@ -2699,43 +3367,43 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>What we found</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Why it mattered</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>What we did</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="24.85" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>H1</t>
@@ -2809,7 +3477,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="24.85" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>H3</t>
@@ -2920,7 +3588,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="24.85" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>H6</t>
@@ -2957,7 +3625,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="24.85" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>H7</t>
@@ -2994,7 +3662,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="24.85" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>H8</t>
@@ -3031,7 +3699,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="24.85" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>H9</t>
@@ -3142,7 +3810,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="24.85" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>H12</t>
@@ -3179,7 +3847,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="24.85" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>H13</t>
@@ -3253,7 +3921,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="37.3" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>H15</t>
@@ -3314,21 +3982,20 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007F7F7F"/>
+    <tabColor rgb="FF7F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.55"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Timeline — from handover to today</t>
@@ -3343,27 +4010,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>When</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3586,7 +4253,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n"/>
+      <c r="A13" s="10" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
           <t>KT</t>
@@ -3608,7 +4275,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="24.85" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
@@ -3743,7 +4410,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="24.85" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>20 Sep 2026</t>
@@ -3851,7 +4518,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="24.85" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>22 Sep 2026</t>
@@ -3878,7 +4545,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="37.3" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026</t>
@@ -3905,7 +4572,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="37.3" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>23 Sep 2026</t>
@@ -3940,23 +4607,20 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
+    <tabColor rgb="FF2E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.55"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="3" max="5"/>
+    <col width="20" customWidth="1" min="6" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Competitive Benchmark — PLM / PPM vendors (team research)</t>
@@ -3971,37 +4635,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Capability</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Our product</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Planview</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Oracle PLM</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>SAP PLM</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Siemens Teamcenter</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Salsify</t>
         </is>
@@ -4451,8 +5115,8 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="18" ht="15.4" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Caveats</t>
         </is>
@@ -4469,11 +5133,11 @@
           <t>Full PLM engineering is out of scope for this product (Overview → Scope), yet four of the five comparators are PLM systems.</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="18" t="n"/>
-      <c r="G19" s="19" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -4486,11 +5150,11 @@
           <t>Our product is rated on potential ('Strong potential', 'Core'); competitors on current capability — not like-for-like.</t>
         </is>
       </c>
-      <c r="C20" s="18" t="n"/>
-      <c r="D20" s="18" t="n"/>
-      <c r="E20" s="18" t="n"/>
-      <c r="F20" s="18" t="n"/>
-      <c r="G20" s="19" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -4503,11 +5167,11 @@
           <t>Three rating scales are mixed (✅ / Strong / Partial). The 'AI recommendations' row reads 'AI' for everyone.</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="n"/>
-      <c r="E21" s="18" t="n"/>
-      <c r="F21" s="18" t="n"/>
-      <c r="G21" s="19" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -4520,14 +5184,14 @@
           <t>Sources are vendor product pages. The Planview link points to Oracle's PLM page; Salsify has no source.</t>
         </is>
       </c>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="18" t="n"/>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
-      <c r="G22" s="19" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="9" t="n"/>
+    </row>
+    <row r="24" ht="15.4" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Positioning (team's diagram)</t>
         </is>
@@ -4544,11 +5208,11 @@
           <t>PLM (Siemens Teamcenter, SAP PLM, Oracle PLM) and portfolio management (Planview, Oracle) → Product Lifecycle &amp; Portfolio Intelligence → Portfolio Health · Profitability · SKU Rationalization · Launch Readiness · Cost / Risk · SKU Assortment → Signals / AI agents → Decision / recommendation.</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="19" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4565,12 +5229,12 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007F7F7F"/>
+    <tabColor rgb="FF7F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.55"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
@@ -4580,7 +5244,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Links — every document, repository and the live demo</t>
@@ -4595,32 +5259,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>What it covers</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Link / location</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Also at</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>In git?</t>
         </is>
@@ -4642,12 +5306,12 @@
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Google Doc</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Artifact</t>
         </is>
@@ -4674,12 +5338,12 @@
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Google Doc</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Artifact</t>
         </is>
@@ -4706,12 +5370,12 @@
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Google Doc</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Artifact</t>
         </is>
@@ -4738,7 +5402,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Google Drive folder</t>
         </is>
@@ -4750,7 +5414,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="24.85" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Team tracker</t>
@@ -4794,7 +5458,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Miro board</t>
         </is>
@@ -4822,7 +5486,7 @@
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Artifact</t>
         </is>
@@ -4850,7 +5514,7 @@
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Artifact</t>
         </is>
@@ -4878,7 +5542,7 @@
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Artifact</t>
         </is>
@@ -4974,7 +5638,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="24.85" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Project blueprint</t>
@@ -5074,7 +5738,7 @@
           <t>Live</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Vercel</t>
         </is>
@@ -5102,7 +5766,7 @@
           <t>Live</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
@@ -5130,7 +5794,7 @@
           <t>Live</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
@@ -5144,20 +5808,20 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" display="Google Doc" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" display="Artifact" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" display="Google Doc" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" display="Artifact" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" display="Google Doc" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" display="Artifact" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" display="Google Drive folder" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" display="Miro board" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" display="Artifact" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" display="Artifact" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" display="Artifact" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" display="Vercel" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" display="GitHub" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" display="GitHub" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5166,12 +5830,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F3A5F"/>
+    <tabColor rgb="FF1F3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.55"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -5183,8 +5847,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="11" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="36" customWidth="1" min="15" max="15"/>
@@ -5192,7 +5855,7 @@
     <col width="20" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Project Plan — merged</t>
@@ -5206,94 +5869,94 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+    <row r="4" ht="37.3" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Objective</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Key question</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Days (working)</t>
         </is>
       </c>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="L4" s="13" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>End</t>
         </is>
       </c>
-      <c r="M4" s="13" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Date basis</t>
         </is>
       </c>
-      <c r="N4" s="13" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Depends on</t>
         </is>
       </c>
-      <c r="O4" s="13" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Expected outcome / definition of done</t>
         </is>
       </c>
-      <c r="P4" s="13" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Where it actually stands</t>
         </is>
       </c>
-      <c r="Q4" s="13" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="37.3" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>0.1</t>
@@ -5329,17 +5992,17 @@
           <t>Have we understood the product, its data and its personas the way the previous team intended?</t>
         </is>
       </c>
-      <c r="H5" s="7" t="n"/>
+      <c r="H5" s="10" t="n"/>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="J5" s="10" t="n">
+      <c r="J5" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="9">
+      <c r="K5" s="21" t="n"/>
+      <c r="L5" s="20">
         <f>IF(OR(K5="",J5=""),"",WORKDAY(K5,J5-1))</f>
         <v/>
       </c>
@@ -5369,7 +6032,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="37.3" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>0.2</t>
@@ -5419,10 +6082,10 @@
         <f>IF(OR(K6="",L6=""),"",NETWORKDAYS(K6,L6))</f>
         <v/>
       </c>
-      <c r="K6" s="15" t="n">
+      <c r="K6" s="22" t="n">
         <v>46266</v>
       </c>
-      <c r="L6" s="15" t="n">
+      <c r="L6" s="22" t="n">
         <v>46285</v>
       </c>
       <c r="M6" s="5" t="inlineStr">
@@ -5451,7 +6114,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="37.3" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -5487,7 +6150,7 @@
           <t>What problem are we solving? Who is affected? What is explicitly in/out of scope?</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>Team Lead</t>
         </is>
@@ -5501,10 +6164,10 @@
         <f>IF(OR(K7="",L7=""),"",NETWORKDAYS(K7,L7))</f>
         <v/>
       </c>
-      <c r="K7" s="15" t="n">
+      <c r="K7" s="22" t="n">
         <v>46268</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="20">
         <f>L13</f>
         <v/>
       </c>
@@ -5534,7 +6197,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="37.3" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>1.2</t>
@@ -5570,7 +6233,7 @@
           <t>Where does data come from? Where are decisions delayed? Where are workarounds used?</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Business Analyst</t>
         </is>
@@ -5584,8 +6247,8 @@
         <f>IF(OR(K8="",L8=""),"",NETWORKDAYS(K8,L8))</f>
         <v/>
       </c>
-      <c r="K8" s="14" t="n"/>
-      <c r="L8" s="9">
+      <c r="K8" s="21" t="n"/>
+      <c r="L8" s="20">
         <f>L13</f>
         <v/>
       </c>
@@ -5615,7 +6278,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="87" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>1.3</t>
@@ -5651,7 +6314,7 @@
           <t>What does each persona decide? What information does each need?</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Business Analyst</t>
         </is>
@@ -5665,8 +6328,8 @@
         <f>IF(OR(K9="",L9=""),"",NETWORKDAYS(K9,L9))</f>
         <v/>
       </c>
-      <c r="K9" s="14" t="n"/>
-      <c r="L9" s="9">
+      <c r="K9" s="21" t="n"/>
+      <c r="L9" s="20">
         <f>L13</f>
         <v/>
       </c>
@@ -5696,7 +6359,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="49.7" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>1.4</t>
@@ -5732,7 +6395,7 @@
           <t>What are the possible root causes behind slow launches, poor profitability, rationalization gaps and disconnected signals?</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Business Analyst</t>
         </is>
@@ -5742,13 +6405,13 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="J10" s="10" t="n">
+      <c r="J10" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="K10" s="15" t="n">
+      <c r="K10" s="22" t="n">
         <v>46288</v>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="20">
         <f>IF(OR(K10="",J10=""),"",WORKDAY(K10,J10-1))</f>
         <v/>
       </c>
@@ -5778,7 +6441,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="37.3" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>1.5</t>
@@ -5814,7 +6477,7 @@
           <t>What industry practices and benchmarks can validate/refine the problem?</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Research Owner</t>
         </is>
@@ -5828,8 +6491,8 @@
         <f>IF(OR(K11="",L11=""),"",NETWORKDAYS(K11,L11))</f>
         <v/>
       </c>
-      <c r="K11" s="14" t="n"/>
-      <c r="L11" s="15" t="n">
+      <c r="K11" s="21" t="n"/>
+      <c r="L11" s="22" t="n">
         <v>46282</v>
       </c>
       <c r="M11" s="5" t="inlineStr">
@@ -5858,7 +6521,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="24.85" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>1.6</t>
@@ -5894,7 +6557,7 @@
           <t>What is the specific root cause? Which pain point is most important?</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>Team Lead</t>
         </is>
@@ -5904,14 +6567,14 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="J12" s="10" t="n">
+      <c r="J12" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="20">
         <f>WORKDAY(MAX(L10,L13),1)</f>
         <v/>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="20">
         <f>IF(OR(K12="",J12=""),"",WORKDAY(K12,J12-1))</f>
         <v/>
       </c>
@@ -5941,7 +6604,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="24.85" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -5977,19 +6640,19 @@
           <t>Is this a demo asset or a product, and what does the brief really require?</t>
         </is>
       </c>
-      <c r="H13" s="7" t="n"/>
+      <c r="H13" s="10" t="n"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J13" s="10" t="n">
+      <c r="J13" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="K13" s="15" t="n">
+      <c r="K13" s="22" t="n">
         <v>46288</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="20">
         <f>IF(OR(K13="",J13=""),"",WORKDAY(K13,J13-1))</f>
         <v/>
       </c>
@@ -6019,81 +6682,81 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="24.85" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>P1 · Business Understanding &amp; SPS</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>Gate</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>Gate 1 — End of SPS</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>Team tracker</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>Validated problem + issue tree + personas + research findings</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="12" t="n"/>
+      <c r="H14" s="16" t="n"/>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="17" t="n"/>
-      <c r="L14" s="17">
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="23" t="n"/>
+      <c r="L14" s="23">
         <f>L12</f>
         <v/>
       </c>
-      <c r="M14" s="12" t="inlineStr">
+      <c r="M14" s="16" t="inlineStr">
         <is>
           <t>Tentative</t>
         </is>
       </c>
-      <c r="N14" s="12" t="inlineStr">
+      <c r="N14" s="16" t="inlineStr">
         <is>
           <t>1.1–1.7</t>
         </is>
       </c>
-      <c r="O14" s="12" t="inlineStr">
+      <c r="O14" s="16" t="inlineStr">
         <is>
           <t>Validated problem + issue tree + personas + research findings</t>
         </is>
       </c>
-      <c r="P14" s="12" t="inlineStr">
+      <c r="P14" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q14" s="12" t="inlineStr">
+      <c r="Q14" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="24.85" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -6129,7 +6792,7 @@
           <t>What decision should the user make after seeing the insight?</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Business Analyst</t>
         </is>
@@ -6139,14 +6802,14 @@
           <t>In progress</t>
         </is>
       </c>
-      <c r="J15" s="10" t="n">
+      <c r="J15" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="20">
         <f>WORKDAY(L14,1)</f>
         <v/>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="20">
         <f>IF(OR(K15="",J15=""),"",WORKDAY(K15,J15-1))</f>
         <v/>
       </c>
@@ -6176,7 +6839,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="24.85" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>2.2</t>
@@ -6212,7 +6875,7 @@
           <t>What should each tab show and what decision does it enable?</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>Product Owner</t>
         </is>
@@ -6222,14 +6885,14 @@
           <t>In progress</t>
         </is>
       </c>
-      <c r="J16" s="10" t="n">
+      <c r="J16" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="20">
         <f>WORKDAY(L14,1)</f>
         <v/>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="20">
         <f>IF(OR(K16="",J16=""),"",WORKDAY(K16,J16-1))</f>
         <v/>
       </c>
@@ -6259,7 +6922,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="37.3" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -6295,7 +6958,7 @@
           <t>How will Margin, Time-to-Market, Launch Success, SKU Productivity, Complexity and Cannibalization be measured?</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>Analytics Lead</t>
         </is>
@@ -6305,14 +6968,14 @@
           <t>In progress</t>
         </is>
       </c>
-      <c r="J17" s="10" t="n">
+      <c r="J17" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="20">
         <f>WORKDAY(L14,1)</f>
         <v/>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="20">
         <f>IF(OR(K17="",J17=""),"",WORKDAY(K17,J17-1))</f>
         <v/>
       </c>
@@ -6342,7 +7005,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="24.85" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>2.4</t>
@@ -6392,8 +7055,8 @@
         <f>IF(OR(K18="",L18=""),"",NETWORKDAYS(K18,L18))</f>
         <v/>
       </c>
-      <c r="K18" s="14" t="n"/>
-      <c r="L18" s="15" t="n">
+      <c r="K18" s="21" t="n"/>
+      <c r="L18" s="22" t="n">
         <v>46279</v>
       </c>
       <c r="M18" s="5" t="inlineStr">
@@ -6422,7 +7085,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="24.85" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -6458,7 +7121,7 @@
           <t>What conditions trigger GO/REVIEW/DELAY or retain/grow/bundle/reposition/sunset?</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>Analytics Lead</t>
         </is>
@@ -6468,14 +7131,14 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="J19" s="10" t="n">
+      <c r="J19" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="20">
         <f>WORKDAY(L17,1)</f>
         <v/>
       </c>
-      <c r="L19" s="9">
+      <c r="L19" s="20">
         <f>IF(OR(K19="",J19=""),"",WORKDAY(K19,J19-1))</f>
         <v/>
       </c>
@@ -6505,7 +7168,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="37.3" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>2.6</t>
@@ -6541,7 +7204,7 @@
           <t>What should remain human-led? What can AI analyze? What can agents monitor/recommend?</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>AI Lead</t>
         </is>
@@ -6551,14 +7214,14 @@
           <t>In progress</t>
         </is>
       </c>
-      <c r="J20" s="10" t="n">
+      <c r="J20" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="20">
         <f>WORKDAY(L14,1)</f>
         <v/>
       </c>
-      <c r="L20" s="9">
+      <c r="L20" s="20">
         <f>IF(OR(K20="",J20=""),"",WORKDAY(K20,J20-1))</f>
         <v/>
       </c>
@@ -6588,7 +7251,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="24.85" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>2.7</t>
@@ -6624,20 +7287,20 @@
           <t>What runs where, and what does it cost?</t>
         </is>
       </c>
-      <c r="H21" s="7" t="n"/>
+      <c r="H21" s="10" t="n"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="J21" s="10" t="n">
+      <c r="J21" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="20">
         <f>WORKDAY(L14,1)</f>
         <v/>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="20">
         <f>IF(OR(K21="",J21=""),"",WORKDAY(K21,J21-1))</f>
         <v/>
       </c>
@@ -6667,7 +7330,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="49.7" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>2.8</t>
@@ -6703,20 +7366,20 @@
           <t>Does each tab lead its persona from insight to decision?</t>
         </is>
       </c>
-      <c r="H22" s="7" t="n"/>
+      <c r="H22" s="10" t="n"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J22" s="10" t="n">
+      <c r="J22" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="20">
         <f>WORKDAY(L16,1)</f>
         <v/>
       </c>
-      <c r="L22" s="9">
+      <c r="L22" s="20">
         <f>IF(OR(K22="",J22=""),"",WORKDAY(K22,J22-1))</f>
         <v/>
       </c>
@@ -6746,81 +7409,81 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="23" ht="24.85" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>P2 · Solution Definition</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>Gate</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>Gate 2 — Solution design complete</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>Team tracker</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>Five modules + KPI dictionary + data model + business rules</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H23" s="12" t="n"/>
+      <c r="H23" s="16" t="n"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J23" s="12" t="n"/>
-      <c r="K23" s="17" t="n"/>
-      <c r="L23" s="17">
+      <c r="J23" s="16" t="n"/>
+      <c r="K23" s="23" t="n"/>
+      <c r="L23" s="23">
         <f>MAX(L15,L16,L17,L19,L20,L21,L22)</f>
         <v/>
       </c>
-      <c r="M23" s="12" t="inlineStr">
+      <c r="M23" s="16" t="inlineStr">
         <is>
           <t>Tentative</t>
         </is>
       </c>
-      <c r="N23" s="12" t="inlineStr">
+      <c r="N23" s="16" t="inlineStr">
         <is>
           <t>2.1–2.8</t>
         </is>
       </c>
-      <c r="O23" s="12" t="inlineStr">
+      <c r="O23" s="16" t="inlineStr">
         <is>
           <t>Five modules + KPI dictionary + data model + business rules</t>
         </is>
       </c>
-      <c r="P23" s="12" t="inlineStr">
+      <c r="P23" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q23" s="12" t="inlineStr">
+      <c r="Q23" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="24.85" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>3.1</t>
@@ -6870,10 +7533,10 @@
         <f>IF(OR(K24="",L24=""),"",NETWORKDAYS(K24,L24))</f>
         <v/>
       </c>
-      <c r="K24" s="15" t="n">
+      <c r="K24" s="22" t="n">
         <v>46274</v>
       </c>
-      <c r="L24" s="15" t="n">
+      <c r="L24" s="22" t="n">
         <v>46279</v>
       </c>
       <c r="M24" s="5" t="inlineStr">
@@ -6902,7 +7565,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="24.85" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>3.1a</t>
@@ -6952,10 +7615,10 @@
         <f>IF(OR(K25="",L25=""),"",NETWORKDAYS(K25,L25))</f>
         <v/>
       </c>
-      <c r="K25" s="15" t="n">
+      <c r="K25" s="22" t="n">
         <v>46279</v>
       </c>
-      <c r="L25" s="15" t="n">
+      <c r="L25" s="22" t="n">
         <v>46285</v>
       </c>
       <c r="M25" s="5" t="inlineStr">
@@ -6984,7 +7647,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="24.85" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>3.1b</t>
@@ -7020,20 +7683,20 @@
           <t>Do the 16 checks pass in SQL too?</t>
         </is>
       </c>
-      <c r="H26" s="7" t="n"/>
+      <c r="H26" s="10" t="n"/>
       <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J26" s="10" t="n">
+      <c r="J26" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="20">
         <f>WORKDAY(L17,1)</f>
         <v/>
       </c>
-      <c r="L26" s="9">
+      <c r="L26" s="20">
         <f>IF(OR(K26="",J26=""),"",WORKDAY(K26,J26-1))</f>
         <v/>
       </c>
@@ -7063,7 +7726,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="87" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>3.1c</t>
@@ -7099,20 +7762,20 @@
           <t>Does any figure disagree between screens?</t>
         </is>
       </c>
-      <c r="H27" s="7" t="n"/>
+      <c r="H27" s="10" t="n"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="J27" s="10" t="n">
+      <c r="J27" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="20">
         <f>WORKDAY(L17,1)</f>
         <v/>
       </c>
-      <c r="L27" s="9">
+      <c r="L27" s="20">
         <f>IF(OR(K27="",J27=""),"",WORKDAY(K27,J27-1))</f>
         <v/>
       </c>
@@ -7142,7 +7805,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="37.3" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>3.1d</t>
@@ -7178,20 +7841,20 @@
           <t>Could a client recognise a real brand on screen?</t>
         </is>
       </c>
-      <c r="H28" s="7" t="n"/>
+      <c r="H28" s="10" t="n"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J28" s="10" t="n">
+      <c r="J28" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="20">
         <f>WORKDAY(L13,1)</f>
         <v/>
       </c>
-      <c r="L28" s="9">
+      <c r="L28" s="20">
         <f>IF(OR(K28="",J28=""),"",WORKDAY(K28,J28-1))</f>
         <v/>
       </c>
@@ -7221,7 +7884,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="37.3" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -7257,7 +7920,7 @@
           <t>Can the VP identify healthy and underperforming products quickly?</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>UI/BI Lead</t>
         </is>
@@ -7267,12 +7930,12 @@
           <t>Rework needed</t>
         </is>
       </c>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="9">
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="20">
         <f>WORKDAY(L23,1)</f>
         <v/>
       </c>
-      <c r="L29" s="9">
+      <c r="L29" s="20">
         <f>IF(OR(K29="",J29=""),"",WORKDAY(K29,J29-1))</f>
         <v/>
       </c>
@@ -7302,7 +7965,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="37.3" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
@@ -7338,7 +8001,7 @@
           <t>Can the user identify launch risks and readiness status?</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>UI/BI Lead</t>
         </is>
@@ -7348,12 +8011,12 @@
           <t>Rework needed</t>
         </is>
       </c>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="9">
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="20">
         <f>WORKDAY(L23,1)</f>
         <v/>
       </c>
-      <c r="L30" s="9">
+      <c r="L30" s="20">
         <f>IF(OR(K30="",J30=""),"",WORKDAY(K30,J30-1))</f>
         <v/>
       </c>
@@ -7383,7 +8046,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="37.3" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
@@ -7419,7 +8082,7 @@
           <t>Can the user explain why profitability is changing?</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>Analytics/UI Lead</t>
         </is>
@@ -7429,12 +8092,12 @@
           <t>Rework needed</t>
         </is>
       </c>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="9">
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="20">
         <f>WORKDAY(L23,1)</f>
         <v/>
       </c>
-      <c r="L31" s="9">
+      <c r="L31" s="20">
         <f>IF(OR(K31="",J31=""),"",WORKDAY(K31,J31-1))</f>
         <v/>
       </c>
@@ -7464,7 +8127,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="37.3" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>3.5</t>
@@ -7500,7 +8163,7 @@
           <t>Can the user simulate portfolio changes and see revenue/margin/complexity impact?</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>Analytics/UI Lead</t>
         </is>
@@ -7510,12 +8173,12 @@
           <t>Rework needed</t>
         </is>
       </c>
-      <c r="J32" s="6" t="n"/>
-      <c r="K32" s="9">
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="20">
         <f>WORKDAY(L23,1)</f>
         <v/>
       </c>
-      <c r="L32" s="9">
+      <c r="L32" s="20">
         <f>IF(OR(K32="",J32=""),"",WORKDAY(K32,J32-1))</f>
         <v/>
       </c>
@@ -7545,7 +8208,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="37.3" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>3.6</t>
@@ -7581,7 +8244,7 @@
           <t>Can external signals influence portfolio decisions?</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>UI/BI Lead</t>
         </is>
@@ -7591,12 +8254,12 @@
           <t>Rework needed</t>
         </is>
       </c>
-      <c r="J33" s="6" t="n"/>
-      <c r="K33" s="9">
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="20">
         <f>WORKDAY(L23,1)</f>
         <v/>
       </c>
-      <c r="L33" s="9">
+      <c r="L33" s="20">
         <f>IF(OR(K33="",J33=""),"",WORKDAY(K33,J33-1))</f>
         <v/>
       </c>
@@ -7626,7 +8289,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="37.3" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>3.7</t>
@@ -7662,20 +8325,20 @@
           <t>Can each persona do their job in five tabs?</t>
         </is>
       </c>
-      <c r="H34" s="7" t="n"/>
+      <c r="H34" s="10" t="n"/>
       <c r="I34" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J34" s="10" t="n">
+      <c r="J34" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="K34" s="9">
+      <c r="K34" s="20">
         <f>WORKDAY(L22,1)</f>
         <v/>
       </c>
-      <c r="L34" s="9">
+      <c r="L34" s="20">
         <f>IF(OR(K34="",J34=""),"",WORKDAY(K34,J34-1))</f>
         <v/>
       </c>
@@ -7705,7 +8368,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="24.85" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>3.8</t>
@@ -7741,20 +8404,20 @@
           <t>Does every figure on screen have one definition and one source?</t>
         </is>
       </c>
-      <c r="H35" s="7" t="n"/>
+      <c r="H35" s="10" t="n"/>
       <c r="I35" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J35" s="10" t="n">
+      <c r="J35" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="K35" s="9">
+      <c r="K35" s="20">
         <f>WORKDAY(MAX(L17,L21),1)</f>
         <v/>
       </c>
-      <c r="L35" s="9">
+      <c r="L35" s="20">
         <f>IF(OR(K35="",J35=""),"",WORKDAY(K35,J35-1))</f>
         <v/>
       </c>
@@ -7784,7 +8447,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="24.85" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>3.9</t>
@@ -7820,20 +8483,20 @@
           <t>Is any figure still hardcoded?</t>
         </is>
       </c>
-      <c r="H36" s="7" t="n"/>
+      <c r="H36" s="10" t="n"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J36" s="10" t="n">
+      <c r="J36" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="K36" s="9">
+      <c r="K36" s="20">
         <f>WORKDAY(MAX(L35,L34),1)</f>
         <v/>
       </c>
-      <c r="L36" s="9">
+      <c r="L36" s="20">
         <f>IF(OR(K36="",J36=""),"",WORKDAY(K36,J36-1))</f>
         <v/>
       </c>
@@ -7863,81 +8526,81 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+    <row r="37" ht="24.85" customHeight="1">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>P3 · Data &amp; Prototype</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>Gate</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>Gate 3 — Functional prototype</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>Team tracker</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>Five tabs working without AI dependency</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="G37" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H37" s="12" t="n"/>
+      <c r="H37" s="16" t="n"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J37" s="12" t="n"/>
-      <c r="K37" s="17" t="n"/>
-      <c r="L37" s="17">
+      <c r="J37" s="16" t="n"/>
+      <c r="K37" s="23" t="n"/>
+      <c r="L37" s="23">
         <f>MAX(L26,L27,L28,L29,L30,L31,L32,L33,L34,L36)</f>
         <v/>
       </c>
-      <c r="M37" s="12" t="inlineStr">
+      <c r="M37" s="16" t="inlineStr">
         <is>
           <t>Tentative</t>
         </is>
       </c>
-      <c r="N37" s="12" t="inlineStr">
+      <c r="N37" s="16" t="inlineStr">
         <is>
           <t>3.1b–3.9</t>
         </is>
       </c>
-      <c r="O37" s="12" t="inlineStr">
+      <c r="O37" s="16" t="inlineStr">
         <is>
           <t>Five tabs working without AI dependency</t>
         </is>
       </c>
-      <c r="P37" s="12" t="inlineStr">
+      <c r="P37" s="16" t="inlineStr">
         <is>
           <t>Excludes 3.2–3.6 until they have estimates, so this date is optimistic (R21).</t>
         </is>
       </c>
-      <c r="Q37" s="12" t="inlineStr">
+      <c r="Q37" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="24.85" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
@@ -7973,7 +8636,7 @@
           <t>What does each agent monitor, analyze, recommend and hand off?</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>AI Lead</t>
         </is>
@@ -7983,14 +8646,14 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="J38" s="10" t="n">
+      <c r="J38" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="K38" s="9">
+      <c r="K38" s="20">
         <f>WORKDAY(L23,1)</f>
         <v/>
       </c>
-      <c r="L38" s="9">
+      <c r="L38" s="20">
         <f>IF(OR(K38="",J38=""),"",WORKDAY(K38,J38-1))</f>
         <v/>
       </c>
@@ -8020,7 +8683,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="24.85" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
@@ -8056,7 +8719,7 @@
           <t>Do recommendations lead to an actionable decision?</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>AI/Tech Lead</t>
         </is>
@@ -8066,14 +8729,14 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="J39" s="10" t="n">
+      <c r="J39" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="K39" s="9">
+      <c r="K39" s="20">
         <f>WORKDAY(MAX(L35,L38),1)</f>
         <v/>
       </c>
-      <c r="L39" s="9">
+      <c r="L39" s="20">
         <f>IF(OR(K39="",J39=""),"",WORKDAY(K39,J39-1))</f>
         <v/>
       </c>
@@ -8103,7 +8766,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="24.85" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
@@ -8139,7 +8802,7 @@
           <t>Can a VP move from insight to action in one flow?</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>QA + Product</t>
         </is>
@@ -8149,14 +8812,14 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="J40" s="10" t="n">
+      <c r="J40" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="K40" s="9">
+      <c r="K40" s="20">
         <f>WORKDAY(MAX(L37,L39),1)</f>
         <v/>
       </c>
-      <c r="L40" s="9">
+      <c r="L40" s="20">
         <f>IF(OR(K40="",J40=""),"",WORKDAY(K40,J40-1))</f>
         <v/>
       </c>
@@ -8186,7 +8849,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="24.85" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -8222,7 +8885,7 @@
           <t>Are the outputs understandable and defensible?</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>QA Lead</t>
         </is>
@@ -8232,14 +8895,14 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="J41" s="10" t="n">
+      <c r="J41" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="K41" s="9">
+      <c r="K41" s="20">
         <f>WORKDAY(L40,1)</f>
         <v/>
       </c>
-      <c r="L41" s="9">
+      <c r="L41" s="20">
         <f>IF(OR(K41="",J41=""),"",WORKDAY(K41,J41-1))</f>
         <v/>
       </c>
@@ -8269,7 +8932,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="24.85" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
@@ -8305,7 +8968,7 @@
           <t>Does every tab earn its place and support a decision?</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>Team Lead</t>
         </is>
@@ -8315,14 +8978,14 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="J42" s="10" t="n">
+      <c r="J42" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="K42" s="9">
+      <c r="K42" s="20">
         <f>WORKDAY(L41,1)</f>
         <v/>
       </c>
-      <c r="L42" s="9">
+      <c r="L42" s="20">
         <f>IF(OR(K42="",J42=""),"",WORKDAY(K42,J42-1))</f>
         <v/>
       </c>
@@ -8352,7 +9015,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="24.85" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
           <t>4.6</t>
@@ -8388,7 +9051,7 @@
           <t>What remains unresolved? Are all scope/KPI/agent requirements covered?</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>Team Lead</t>
         </is>
@@ -8398,14 +9061,14 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="J43" s="10" t="n">
+      <c r="J43" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="K43" s="9">
+      <c r="K43" s="20">
         <f>IF(COUNT(L42,L44)=0,"",WORKDAY(MAX(L42,L44),1))</f>
         <v/>
       </c>
-      <c r="L43" s="9">
+      <c r="L43" s="20">
         <f>IF(OR(K43="",J43=""),"",WORKDAY(K43,J43-1))</f>
         <v/>
       </c>
@@ -8435,7 +9098,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="24.85" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>4.7</t>
@@ -8471,18 +9134,18 @@
           <t>Is the demo URL stable and the data current?</t>
         </is>
       </c>
-      <c r="H44" s="7" t="n"/>
+      <c r="H44" s="10" t="n"/>
       <c r="I44" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
       <c r="J44" s="5" t="n"/>
-      <c r="K44" s="9">
+      <c r="K44" s="20">
         <f>WORKDAY(L41,1)</f>
         <v/>
       </c>
-      <c r="L44" s="9">
+      <c r="L44" s="20">
         <f>IF(OR(K44="",J44=""),"",WORKDAY(K44,J44-1))</f>
         <v/>
       </c>
@@ -8512,81 +9175,81 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+    <row r="45" ht="24.85" customHeight="1">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>P4 · AI, Testing &amp; Final Demo</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>Gate</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>Gate 4 — Final demo</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="16" t="inlineStr">
         <is>
           <t>Team tracker</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F45" s="16" t="inlineStr">
         <is>
           <t>Agents + simulation + testing + VP decision journey</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="G45" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H45" s="12" t="n"/>
+      <c r="H45" s="16" t="n"/>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="J45" s="12" t="n"/>
-      <c r="K45" s="17" t="n"/>
-      <c r="L45" s="17">
+      <c r="J45" s="16" t="n"/>
+      <c r="K45" s="23" t="n"/>
+      <c r="L45" s="23">
         <f>IF(L43="","",WORKDAY(L43,1))</f>
         <v/>
       </c>
-      <c r="M45" s="12" t="inlineStr">
+      <c r="M45" s="16" t="inlineStr">
         <is>
           <t>Tentative</t>
         </is>
       </c>
-      <c r="N45" s="12" t="inlineStr">
+      <c r="N45" s="16" t="inlineStr">
         <is>
           <t>4.1–4.7, Q9</t>
         </is>
       </c>
-      <c r="O45" s="12" t="inlineStr">
+      <c r="O45" s="16" t="inlineStr">
         <is>
           <t>Agents + simulation + testing + VP decision journey</t>
         </is>
       </c>
-      <c r="P45" s="12" t="inlineStr">
+      <c r="P45" s="16" t="inlineStr">
         <is>
           <t>No deadline set (confirmed 22 Sep). This is the earliest date at the durations above.</t>
         </is>
       </c>
-      <c r="Q45" s="12" t="inlineStr">
+      <c r="Q45" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="24.85" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -8622,18 +9285,18 @@
           <t>What does the agreed positioning need next?</t>
         </is>
       </c>
-      <c r="H46" s="7" t="n"/>
+      <c r="H46" s="10" t="n"/>
       <c r="I46" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
       <c r="J46" s="5" t="n"/>
-      <c r="K46" s="9">
+      <c r="K46" s="20">
         <f>IF(L45="","",WORKDAY(L45,1))</f>
         <v/>
       </c>
-      <c r="L46" s="9">
+      <c r="L46" s="20">
         <f>IF(OR(K46="",J46=""),"",WORKDAY(K46,J46-1))</f>
         <v/>
       </c>
@@ -8705,12 +9368,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00548235"/>
+    <tabColor rgb="FF548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K36"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.55"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -8720,12 +9383,11 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="9" max="10"/>
     <col width="44" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Daily Task Log</t>
@@ -8740,63 +9402,63 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Team Member</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Workstream / Module</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Task / Activity</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>What Needs to Be Done</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Dependency / Blocker</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Planned EOD</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Actual EOD</t>
         </is>
       </c>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="24.85" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>18 May 2026</t>
@@ -8853,7 +9515,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="37.3" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>21 May – 27 Jul 2026</t>
@@ -8910,7 +9572,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="24.85" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
@@ -8967,7 +9629,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="24.85" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
@@ -9020,7 +9682,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr"/>
     </row>
-    <row r="9">
+    <row r="9" ht="24.85" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
@@ -9073,7 +9735,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr"/>
     </row>
-    <row r="10">
+    <row r="10" ht="37.3" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>9 Sep 2026</t>
@@ -9130,7 +9792,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="24.85" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>14 Sep 2026</t>
@@ -9187,7 +9849,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="24.85" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>14 Sep 2026</t>
@@ -9297,7 +9959,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="24.85" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
@@ -9350,7 +10012,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr"/>
     </row>
-    <row r="15">
+    <row r="15" ht="24.85" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
@@ -9403,7 +10065,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr"/>
     </row>
-    <row r="16">
+    <row r="16" ht="24.85" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>20 Sep 2026</t>
@@ -9460,7 +10122,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="24.85" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>20 Sep 2026</t>
@@ -9517,7 +10179,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="24.85" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>20 Sep 2026</t>
@@ -9574,7 +10236,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="24.85" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>20 Sep 2026</t>
@@ -9631,7 +10293,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="24.85" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>20 Sep 2026</t>
@@ -9688,7 +10350,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="24.85" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>21 Sep 2026</t>
@@ -9741,7 +10403,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr"/>
     </row>
-    <row r="22">
+    <row r="22" ht="37.3" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>22 Sep 2026</t>
@@ -9798,7 +10460,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="24.85" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>23 Sep 2026</t>
@@ -9851,7 +10513,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr"/>
     </row>
-    <row r="24">
+    <row r="24" ht="24.85" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>23 Sep 2026</t>
@@ -9908,7 +10570,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="37.3" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>23 Sep 2026</t>
@@ -9965,7 +10627,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="24.85" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>24 Sep 2026</t>
@@ -10076,6 +10738,519 @@
       <c r="K27" s="5" t="inlineStr">
         <is>
           <t>This sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>29 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Guna</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Database Integration</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>O1 threshold audit — dollar-cutoff calibration</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Decide and implement how hand-tuned dollar thresholds (Netherlands / France-Austria-Poland catalog cutoffs, Introduction-stage lifecycle cutoff) should be rescaled now that real per-SKU revenue is live — verify selectivity is preserved, not just unit-converted</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Live SKU revenue (skuRevenueM)</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>Mean-ratio rescale was wrong for SKUHoldingsMatrix — real revenue is Pareto-skewed vs. the old uniform hand-typed values; caught by checking selectivity numerically, fixed with rank-preserving constants instead</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Guna</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Branding / UI</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Extract and wire the product logo</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Crop the cube mark from the reference Logo.png, produce header / login / favicon assets, replace placeholder icons in Header, LoginPage and WelcomeGate</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Logo.png reference image</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Also replaced WelcomeGate’s generic "AI network lines" background with a product-lifecycle-curve motif matching the brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Guna</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>UI / Navigation</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Convert "Switch profile" into an inline dropdown</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Replace the full-screen navigate-back-to-Welcome-Gate flow with an in-header role picker so switching persona no longer leaves the current tab</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Removed the now-dead handleSwitchPersona / onSwitchPersona plumbing it replaced</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Guna</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Product Research</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Review daily team call; audit Top-Down Drilldown against the database</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Check whether the OTIF / fulfillment drill-down (LATAM / EMEA / APAC) the team reviewed live on the call is backed by real data</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Database connected (29 Sep)</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Found the regions, managers and OTIF numbers shown are entirely fictional — the DB only has 7 European countries; real lead-time / stockout signals exist but are not wired to this screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Guna</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Product Research</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Decide real vs. illustrative regions for the drill-down</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Choose whether Top-Down Drilldown should be relabeled to the DB’s real 7 countries / 3 European regions, or stay APAC / EMEA / LATAM as demo framing</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Team decision</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Blocks defining a real OTIF metric; raised in the 30 Sep call</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Guna</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Metrics / Backend</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Define and compute a real OTIF metric</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>fact_sales only has stock_out_flag and lead_time_days, not literal ordered-vs-received quantities — pick a derivable definition and add it as a SQL function, same pattern as the other live metrics</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Region decision (row above)</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Raised in the 30 Sep call as the model for detect → diagnose → simulate → recommend elsewhere in the app</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Guna</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Frontend / Search</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Bulk multi-SKU search and combined report</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Let a user select several SKUs at once (not just one at a time) and generate a single combined report</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed missing app-wide; raised in the 30 Sep call</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Guna</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Report download / export</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Confirm and, if missing, add a way to download what is on screen — currently only scattered per-tab CSV buttons exist (SKU Performance, Rationalization)</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>Left as an open question in the 30 Sep call</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Guna</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Codebase Remediation</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>O1 threshold audit — percent constants</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Wire the hand-tuned % constants (cannibalization uplift, waste write-off, complexity savings, etc.) to live revenue inputs; the constants themselves stay as-is per the 29 Sep decision</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Live skuRevenueM in the affected files</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>Decided 29 Sep: treat as demo-plausible assumptions, no recalibration needed — just needs wiring</t>
         </is>
       </c>
     </row>
@@ -10121,17 +11296,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00BF8F00"/>
+    <tabColor rgb="FFBF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.55"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -10141,7 +11315,7 @@
     <col width="36" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Open Questions — decisions we need</t>
@@ -10156,63 +11330,63 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Why it matters</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Default if unanswered</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Who answers</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Meeting</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Needed by</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Answer / decision</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="37.3" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Q1</t>
@@ -10255,7 +11429,7 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="20">
         <f>IFERROR(IF(INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H5,2),'Stakeholder Meetings'!$A$5:$A$12,0))="","",INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H5,2),'Stakeholder Meetings'!$A$5:$A$12,0))),"")</f>
         <v/>
       </c>
@@ -10264,9 +11438,9 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K5" s="7" t="n"/>
-    </row>
-    <row r="6">
+      <c r="K5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="24.85" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Q2</t>
@@ -10308,7 +11482,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="20">
         <f>IFERROR(IF(INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H6,2),'Stakeholder Meetings'!$A$5:$A$12,0))="","",INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H6,2),'Stakeholder Meetings'!$A$5:$A$12,0))),"")</f>
         <v/>
       </c>
@@ -10317,9 +11491,9 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K6" s="7" t="n"/>
-    </row>
-    <row r="7">
+      <c r="K6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="37.3" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Q3</t>
@@ -10362,7 +11536,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="20">
         <f>IFERROR(IF(INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H7,2),'Stakeholder Meetings'!$A$5:$A$12,0))="","",INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H7,2),'Stakeholder Meetings'!$A$5:$A$12,0))),"")</f>
         <v/>
       </c>
@@ -10371,9 +11545,9 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K7" s="7" t="n"/>
-    </row>
-    <row r="8">
+      <c r="K7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="24.85" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Q4</t>
@@ -10415,7 +11589,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="20">
         <f>IFERROR(IF(INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H8,2),'Stakeholder Meetings'!$A$5:$A$12,0))="","",INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H8,2),'Stakeholder Meetings'!$A$5:$A$12,0))),"")</f>
         <v/>
       </c>
@@ -10424,9 +11598,9 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K8" s="7" t="n"/>
-    </row>
-    <row r="9">
+      <c r="K8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="24.85" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Q5</t>
@@ -10468,7 +11642,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="20">
         <f>IFERROR(IF(INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H9,2),'Stakeholder Meetings'!$A$5:$A$12,0))="","",INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H9,2),'Stakeholder Meetings'!$A$5:$A$12,0))),"")</f>
         <v/>
       </c>
@@ -10477,9 +11651,9 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K9" s="7" t="n"/>
-    </row>
-    <row r="10">
+      <c r="K9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="37.3" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Q6</t>
@@ -10521,7 +11695,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="20">
         <f>IFERROR(IF(INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H10,2),'Stakeholder Meetings'!$A$5:$A$12,0))="","",INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H10,2),'Stakeholder Meetings'!$A$5:$A$12,0))),"")</f>
         <v/>
       </c>
@@ -10530,9 +11704,9 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K10" s="7" t="n"/>
-    </row>
-    <row r="11">
+      <c r="K10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="74.55" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Q7</t>
@@ -10573,7 +11747,7 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="20">
         <f>IFERROR(IF(INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H11,2),'Stakeholder Meetings'!$A$5:$A$12,0))="","",INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H11,2),'Stakeholder Meetings'!$A$5:$A$12,0))),"")</f>
         <v/>
       </c>
@@ -10582,9 +11756,9 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K11" s="7" t="n"/>
-    </row>
-    <row r="12">
+      <c r="K11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="37.3" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Q8</t>
@@ -10626,7 +11800,7 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="20">
         <f>IFERROR(IF(INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H12,2),'Stakeholder Meetings'!$A$5:$A$12,0))="","",INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H12,2),'Stakeholder Meetings'!$A$5:$A$12,0))),"")</f>
         <v/>
       </c>
@@ -10635,9 +11809,9 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K12" s="7" t="n"/>
-    </row>
-    <row r="13">
+      <c r="K12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="37.3" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Q9</t>
@@ -10678,7 +11852,7 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="20">
         <f>IFERROR(IF(INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H13,2),'Stakeholder Meetings'!$A$5:$A$12,0))="","",INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H13,2),'Stakeholder Meetings'!$A$5:$A$12,0))),"")</f>
         <v/>
       </c>
@@ -10687,9 +11861,9 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K13" s="7" t="n"/>
-    </row>
-    <row r="14">
+      <c r="K13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="24.85" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Q10</t>
@@ -10730,7 +11904,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="20">
         <f>IFERROR(IF(INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H14,2),'Stakeholder Meetings'!$A$5:$A$12,0))="","",INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H14,2),'Stakeholder Meetings'!$A$5:$A$12,0))),"")</f>
         <v/>
       </c>
@@ -10739,9 +11913,9 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K14" s="7" t="n"/>
-    </row>
-    <row r="15">
+      <c r="K14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="24.85" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Q11</t>
@@ -10783,7 +11957,7 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="20">
         <f>IFERROR(IF(INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H15,2),'Stakeholder Meetings'!$A$5:$A$12,0))="","",INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H15,2),'Stakeholder Meetings'!$A$5:$A$12,0))),"")</f>
         <v/>
       </c>
@@ -10792,9 +11966,9 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K15" s="7" t="n"/>
-    </row>
-    <row r="16">
+      <c r="K15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="49.7" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Q12</t>
@@ -10835,7 +12009,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="20">
         <f>IFERROR(IF(INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H16,2),'Stakeholder Meetings'!$A$5:$A$12,0))="","",INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H16,2),'Stakeholder Meetings'!$A$5:$A$12,0))),"")</f>
         <v/>
       </c>
@@ -10844,9 +12018,9 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K16" s="7" t="n"/>
-    </row>
-    <row r="17">
+      <c r="K16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="74.55" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Q13</t>
@@ -10888,7 +12062,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="20">
         <f>IFERROR(IF(INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H17,2),'Stakeholder Meetings'!$A$5:$A$12,0))="","",INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H17,2),'Stakeholder Meetings'!$A$5:$A$12,0))),"")</f>
         <v/>
       </c>
@@ -10897,9 +12071,9 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K17" s="7" t="n"/>
-    </row>
-    <row r="18">
+      <c r="K17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="37.3" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Q14</t>
@@ -10940,7 +12114,7 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="20">
         <f>IFERROR(IF(INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H18,2),'Stakeholder Meetings'!$A$5:$A$12,0))="","",INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H18,2),'Stakeholder Meetings'!$A$5:$A$12,0))),"")</f>
         <v/>
       </c>
@@ -10949,9 +12123,9 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K18" s="7" t="n"/>
-    </row>
-    <row r="19">
+      <c r="K18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="37.3" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Q15</t>
@@ -10994,7 +12168,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="20">
         <f>IFERROR(IF(INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H19,2),'Stakeholder Meetings'!$A$5:$A$12,0))="","",INDEX('Stakeholder Meetings'!$G$5:$G$12,MATCH(LEFT(H19,2),'Stakeholder Meetings'!$A$5:$A$12,0))),"")</f>
         <v/>
       </c>
@@ -11003,7 +12177,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K19" s="7" t="n"/>
+      <c r="K19" s="10" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J5:J19">
@@ -11032,12 +12206,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00BF8F00"/>
+    <tabColor rgb="FFBF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.55"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
@@ -11051,7 +12225,7 @@
     <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Stakeholder Meetings — clearing scope and misunderstandings</t>
@@ -11066,58 +12240,58 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Meeting</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Questions to settle</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Suggested attendees</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Pre-read</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Proposed date</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Length</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Decisions / outcome</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="24.85" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>M8</t>
@@ -11148,7 +12322,7 @@
           <t>This tracker</t>
         </is>
       </c>
-      <c r="G5" s="14" t="n"/>
+      <c r="G5" s="21" t="n"/>
       <c r="H5" s="5" t="inlineStr">
         <is>
           <t>45 min</t>
@@ -11159,9 +12333,9 @@
           <t>Not scheduled</t>
         </is>
       </c>
-      <c r="J5" s="7" t="n"/>
-    </row>
-    <row r="6">
+      <c r="J5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="24.85" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>M1</t>
@@ -11192,7 +12366,7 @@
           <t>pitch.md; Report 3</t>
         </is>
       </c>
-      <c r="G6" s="14" t="n"/>
+      <c r="G6" s="21" t="n"/>
       <c r="H6" s="5" t="inlineStr">
         <is>
           <t>60 min</t>
@@ -11203,9 +12377,9 @@
           <t>Not scheduled</t>
         </is>
       </c>
-      <c r="J6" s="7" t="n"/>
-    </row>
-    <row r="7">
+      <c r="J6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="24.85" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>M2</t>
@@ -11236,7 +12410,7 @@
           <t>Report 1; Gap Analysis tab</t>
         </is>
       </c>
-      <c r="G7" s="14" t="n"/>
+      <c r="G7" s="21" t="n"/>
       <c r="H7" s="5" t="inlineStr">
         <is>
           <t>60 min</t>
@@ -11247,9 +12421,9 @@
           <t>Not scheduled</t>
         </is>
       </c>
-      <c r="J7" s="7" t="n"/>
-    </row>
-    <row r="8">
+      <c r="J7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="24.85" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>M3</t>
@@ -11280,7 +12454,7 @@
           <t>Report 2; Personas &amp; Journey tab</t>
         </is>
       </c>
-      <c r="G8" s="14" t="n"/>
+      <c r="G8" s="21" t="n"/>
       <c r="H8" s="5" t="inlineStr">
         <is>
           <t>45 min</t>
@@ -11291,9 +12465,9 @@
           <t>Not scheduled</t>
         </is>
       </c>
-      <c r="J8" s="7" t="n"/>
-    </row>
-    <row r="9">
+      <c r="J8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="24.85" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>M4</t>
@@ -11324,7 +12498,7 @@
           <t>Architecture Roadmap tab</t>
         </is>
       </c>
-      <c r="G9" s="14" t="n"/>
+      <c r="G9" s="21" t="n"/>
       <c r="H9" s="5" t="inlineStr">
         <is>
           <t>45 min</t>
@@ -11335,9 +12509,9 @@
           <t>Not scheduled</t>
         </is>
       </c>
-      <c r="J9" s="7" t="n"/>
-    </row>
-    <row r="10">
+      <c r="J9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="24.85" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>M5</t>
@@ -11368,7 +12542,7 @@
           <t>Handover Findings tab</t>
         </is>
       </c>
-      <c r="G10" s="14" t="n"/>
+      <c r="G10" s="21" t="n"/>
       <c r="H10" s="5" t="inlineStr">
         <is>
           <t>60 min</t>
@@ -11379,9 +12553,9 @@
           <t>Not scheduled</t>
         </is>
       </c>
-      <c r="J10" s="7" t="n"/>
-    </row>
-    <row r="11">
+      <c r="J10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="24.85" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>M6</t>
@@ -11412,7 +12586,7 @@
           <t>This tracker</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>Weekly</t>
         </is>
@@ -11427,9 +12601,9 @@
           <t>Not scheduled</t>
         </is>
       </c>
-      <c r="J11" s="7" t="n"/>
-    </row>
-    <row r="12">
+      <c r="J11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="24.85" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>M7</t>
@@ -11460,7 +12634,7 @@
           <t>Personas &amp; Journey tab (section C)</t>
         </is>
       </c>
-      <c r="G12" s="14" t="n"/>
+      <c r="G12" s="21" t="n"/>
       <c r="H12" s="5" t="inlineStr">
         <is>
           <t>60 min</t>
@@ -11471,7 +12645,7 @@
           <t>Not scheduled</t>
         </is>
       </c>
-      <c r="J12" s="7" t="n"/>
+      <c r="J12" s="10" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I5:I12">
@@ -11500,27 +12674,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
+    <tabColor rgb="FF2E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.55"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="4" max="6"/>
+    <col width="30" customWidth="1" min="7" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Gap Analysis — requirements backlog</t>
@@ -11534,64 +12705,64 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+    <row r="4" ht="24.85" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>What the existing solution shows</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Recommended improvement</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Decision supported / business impact</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Validation needed</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Team status</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Plan step</t>
         </is>
       </c>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Our note</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="74.55" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -11642,7 +12813,7 @@
       </c>
       <c r="K5" s="5" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="37.3" customHeight="1">
       <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
@@ -11693,7 +12864,7 @@
       </c>
       <c r="K6" s="5" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="49.7" customHeight="1">
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
@@ -11744,7 +12915,7 @@
       </c>
       <c r="K7" s="5" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="37.3" customHeight="1">
       <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
@@ -11795,7 +12966,7 @@
       </c>
       <c r="K8" s="5" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="49.7" customHeight="1">
       <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
@@ -11846,7 +13017,7 @@
       </c>
       <c r="K9" s="5" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="49.7" customHeight="1">
       <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
@@ -11901,7 +13072,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="37.3" customHeight="1">
       <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
@@ -11956,7 +13127,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="49.7" customHeight="1">
       <c r="A12" s="5" t="n">
         <v>8</v>
       </c>
@@ -12011,7 +13182,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="49.7" customHeight="1">
       <c r="A13" s="5" t="n">
         <v>9</v>
       </c>
@@ -12062,7 +13233,7 @@
       </c>
       <c r="K13" s="5" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="37.3" customHeight="1">
       <c r="A14" s="5" t="n">
         <v>10</v>
       </c>
@@ -12113,7 +13284,7 @@
       </c>
       <c r="K14" s="5" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="49.7" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
@@ -12164,7 +13335,7 @@
       </c>
       <c r="K15" s="5" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="49.7" customHeight="1">
       <c r="A16" s="5" t="n">
         <v>12</v>
       </c>
@@ -12215,7 +13386,7 @@
       </c>
       <c r="K16" s="5" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="37.3" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
@@ -12266,7 +13437,7 @@
       </c>
       <c r="K17" s="5" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="49.7" customHeight="1">
       <c r="A18" s="5" t="n">
         <v>14</v>
       </c>
@@ -12317,7 +13488,7 @@
       </c>
       <c r="K18" s="5" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="49.7" customHeight="1">
       <c r="A19" s="5" t="n">
         <v>15</v>
       </c>
@@ -12368,7 +13539,7 @@
       </c>
       <c r="K19" s="5" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="37.3" customHeight="1">
       <c r="A20" s="5" t="n">
         <v>16</v>
       </c>
@@ -12419,7 +13590,7 @@
       </c>
       <c r="K20" s="5" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="49.7" customHeight="1">
       <c r="A21" s="5" t="n">
         <v>17</v>
       </c>
@@ -12470,7 +13641,7 @@
       </c>
       <c r="K21" s="5" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="37.3" customHeight="1">
       <c r="A22" s="5" t="n">
         <v>18</v>
       </c>
@@ -12521,7 +13692,7 @@
       </c>
       <c r="K22" s="5" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="37.3" customHeight="1">
       <c r="A23" s="5" t="n">
         <v>19</v>
       </c>
@@ -12572,7 +13743,7 @@
       </c>
       <c r="K23" s="5" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="37.3" customHeight="1">
       <c r="A24" s="5" t="n">
         <v>20</v>
       </c>
@@ -12623,7 +13794,7 @@
       </c>
       <c r="K24" s="5" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="37.3" customHeight="1">
       <c r="A25" s="5" t="n">
         <v>21</v>
       </c>
@@ -12674,7 +13845,7 @@
       </c>
       <c r="K25" s="5" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="62.15" customHeight="1">
       <c r="A26" s="5" t="n">
         <v>22</v>
       </c>
@@ -12725,7 +13896,7 @@
       </c>
       <c r="K26" s="5" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="37.3" customHeight="1">
       <c r="A27" s="5" t="n">
         <v>23</v>
       </c>
@@ -12776,7 +13947,7 @@
       </c>
       <c r="K27" s="5" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="49.7" customHeight="1">
       <c r="A28" s="5" t="n">
         <v>24</v>
       </c>
@@ -12827,7 +13998,7 @@
       </c>
       <c r="K28" s="5" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" ht="37.3" customHeight="1">
       <c r="A29" s="5" t="n">
         <v>25</v>
       </c>
@@ -12878,7 +14049,7 @@
       </c>
       <c r="K29" s="5" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="37.3" customHeight="1">
       <c r="A30" s="5" t="n">
         <v>26</v>
       </c>
@@ -12929,7 +14100,7 @@
       </c>
       <c r="K30" s="5" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="49.7" customHeight="1">
       <c r="A31" s="5" t="n">
         <v>27</v>
       </c>
@@ -12980,7 +14151,7 @@
       </c>
       <c r="K31" s="5" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="37.3" customHeight="1">
       <c r="A32" s="5" t="n">
         <v>28</v>
       </c>
@@ -13031,7 +14202,7 @@
       </c>
       <c r="K32" s="5" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" ht="24.85" customHeight="1">
       <c r="A33" s="5" t="n">
         <v>29</v>
       </c>
@@ -13082,7 +14253,7 @@
       </c>
       <c r="K33" s="5" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="49.7" customHeight="1">
       <c r="A34" s="5" t="n">
         <v>30</v>
       </c>
@@ -13133,7 +14304,7 @@
       </c>
       <c r="K34" s="5" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="37.3" customHeight="1">
       <c r="A35" s="5" t="n">
         <v>31</v>
       </c>
@@ -13184,7 +14355,7 @@
       </c>
       <c r="K35" s="5" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="37.3" customHeight="1">
       <c r="A36" s="5" t="n">
         <v>32</v>
       </c>
@@ -13239,7 +14410,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="24.85" customHeight="1">
       <c r="A37" s="5" t="n">
         <v>33</v>
       </c>
@@ -13290,7 +14461,7 @@
       </c>
       <c r="K37" s="5" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" ht="37.3" customHeight="1">
       <c r="A38" s="5" t="n">
         <v>34</v>
       </c>
@@ -13345,7 +14516,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="37.3" customHeight="1">
       <c r="A39" s="5" t="n">
         <v>35</v>
       </c>
@@ -13396,7 +14567,7 @@
       </c>
       <c r="K39" s="5" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" ht="37.3" customHeight="1">
       <c r="A40" s="5" t="n">
         <v>36</v>
       </c>
@@ -13451,7 +14622,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="37.3" customHeight="1">
       <c r="A41" s="5" t="n">
         <v>37</v>
       </c>
@@ -13494,7 +14665,7 @@
       </c>
       <c r="K41" s="5" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" ht="24.85" customHeight="1">
       <c r="A42" s="5" t="n">
         <v>38</v>
       </c>
@@ -13537,7 +14708,7 @@
       </c>
       <c r="K42" s="5" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="37.3" customHeight="1">
       <c r="A43" s="5" t="n">
         <v>39</v>
       </c>
@@ -13580,7 +14751,7 @@
       </c>
       <c r="K43" s="5" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="24.85" customHeight="1">
       <c r="A44" s="5" t="n">
         <v>40</v>
       </c>
@@ -13623,7 +14794,7 @@
       </c>
       <c r="K44" s="5" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="24.85" customHeight="1">
       <c r="A45" s="5" t="n">
         <v>41</v>
       </c>
@@ -13666,7 +14837,7 @@
       </c>
       <c r="K45" s="5" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="24.85" customHeight="1">
       <c r="A46" s="5" t="n">
         <v>42</v>
       </c>
@@ -13709,7 +14880,7 @@
       </c>
       <c r="K46" s="5" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="24.85" customHeight="1">
       <c r="A47" s="5" t="n">
         <v>43</v>
       </c>
@@ -13752,7 +14923,7 @@
       </c>
       <c r="K47" s="5" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="24.85" customHeight="1">
       <c r="A48" s="5" t="n">
         <v>44</v>
       </c>
@@ -13813,22 +14984,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
+    <tabColor rgb="FF2E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.55"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Personas &amp; Journey</t>
@@ -13842,35 +15012,35 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="15.4" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>A · Who needs which capability</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Capability</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>VP Product Management</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Product Manager</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Pricing &amp; Margin Partner</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Primary decision</t>
         </is>
@@ -13930,7 +15100,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="24.85" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Profitability</t>
@@ -13957,7 +15127,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="24.85" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SKU Rationalization</t>
@@ -14011,7 +15181,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="24.85" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Decision Intelligence &amp; Orchestration</t>
@@ -14038,41 +15208,41 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="14" ht="15.4" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>B · Current → future decision journey</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="15" ht="24.85" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Capability</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Current process / pain point</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Future capability</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Future decision</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Business outcome</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="24.85" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Portfolio Health</t>
@@ -14099,7 +15269,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="37.3" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Launch Readiness</t>
@@ -14126,7 +15296,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="24.85" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Profitability</t>
@@ -14153,7 +15323,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="24.85" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>SKU Rationalization</t>
@@ -14180,7 +15350,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="24.85" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Signals</t>
@@ -14207,35 +15377,35 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="23" ht="15.4" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>C · End-to-end decision journey (team's Miro board)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+    <row r="24" ht="24.85" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>What happens</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Screens involved today</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Proposed home in the 5-tab target (confirm in M3)</t>
         </is>
@@ -14266,7 +15436,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="24.85" customHeight="1">
       <c r="A26" s="5" t="n">
         <v>2</v>
       </c>
@@ -14291,7 +15461,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="24.85" customHeight="1">
       <c r="A27" s="5" t="n">
         <v>3</v>
       </c>
@@ -14316,7 +15486,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="24.85" customHeight="1">
       <c r="A28" s="5" t="n">
         <v>4</v>
       </c>
@@ -14341,7 +15511,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="24.85" customHeight="1">
       <c r="A29" s="5" t="n">
         <v>5</v>
       </c>
@@ -14441,7 +15611,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="37.3" customHeight="1">
       <c r="A33" s="5" t="n">
         <v>9</v>
       </c>
@@ -14491,7 +15661,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="24.85" customHeight="1">
       <c r="A35" s="5" t="n">
         <v>11</v>
       </c>
@@ -14566,7 +15736,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="24.85" customHeight="1">
       <c r="A38" s="5" t="n">
         <v>14</v>
       </c>
@@ -14597,7 +15767,7 @@
           <t>Miro board</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Open the decision journey</t>
         </is>
@@ -14613,7 +15783,7 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" display="Open the decision journey" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14622,27 +15792,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00C00000"/>
+    <tabColor rgb="FFC00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.55"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="5" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="44" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="10" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Risks &amp; Issues</t>
@@ -14657,63 +15824,63 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Risk or issue</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Consequence</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Likelihood</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Mitigation / next step</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Linked</t>
         </is>
       </c>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="24.85" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>R1</t>
@@ -14769,7 +15936,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="24.85" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>R2</t>
@@ -14860,7 +16027,7 @@
         <f>IF(OR(E7="",F7=""),"",IF((($E7="High")*3+($E7="Medium")*2+($E7="Low")*1)*(($F7="High")*3+($F7="Medium")*2+($F7="Low")*1)&gt;=6,"High",IF((($E7="High")*3+($E7="Medium")*2+($E7="Low")*1)*(($F7="High")*3+($F7="Medium")*2+($F7="Low")*1)&gt;=3,"Medium","Low")))</f>
         <v/>
       </c>
-      <c r="H7" s="7" t="n"/>
+      <c r="H7" s="10" t="n"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Remove the cards unless opex is added</t>
@@ -14877,7 +16044,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="24.85" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>R4</t>
@@ -14912,7 +16079,7 @@
         <f>IF(OR(E8="",F8=""),"",IF((($E8="High")*3+($E8="Medium")*2+($E8="Low")*1)*(($F8="High")*3+($F8="Medium")*2+($F8="Low")*1)&gt;=6,"High",IF((($E8="High")*3+($E8="Medium")*2+($E8="Low")*1)*(($F8="High")*3+($F8="Medium")*2+($F8="Low")*1)&gt;=3,"Medium","Low")))</f>
         <v/>
       </c>
-      <c r="H8" s="7" t="n"/>
+      <c r="H8" s="10" t="n"/>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Synthetic launch table</t>
@@ -14929,7 +16096,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="24.85" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>R5</t>
@@ -14964,7 +16131,7 @@
         <f>IF(OR(E9="",F9=""),"",IF((($E9="High")*3+($E9="Medium")*2+($E9="Low")*1)*(($F9="High")*3+($F9="Medium")*2+($F9="Low")*1)&gt;=6,"High",IF((($E9="High")*3+($E9="Medium")*2+($E9="Low")*1)*(($F9="High")*3+($F9="Medium")*2+($F9="Low")*1)&gt;=3,"Medium","Low")))</f>
         <v/>
       </c>
-      <c r="H9" s="7" t="n"/>
+      <c r="H9" s="10" t="n"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Rename to fictional brands</t>
@@ -15016,7 +16183,7 @@
         <f>IF(OR(E10="",F10=""),"",IF((($E10="High")*3+($E10="Medium")*2+($E10="Low")*1)*(($F10="High")*3+($F10="Medium")*2+($F10="Low")*1)&gt;=6,"High",IF((($E10="High")*3+($E10="Medium")*2+($E10="Low")*1)*(($F10="High")*3+($F10="Medium")*2+($F10="Low")*1)&gt;=3,"Medium","Low")))</f>
         <v/>
       </c>
-      <c r="H10" s="7" t="n"/>
+      <c r="H10" s="10" t="n"/>
       <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Generator constraint plus a validation check</t>
@@ -15033,7 +16200,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="24.85" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>R7</t>
@@ -15089,7 +16256,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="24.85" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>R8</t>
@@ -15201,7 +16368,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="24.85" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>R10</t>
@@ -15236,7 +16403,7 @@
         <f>IF(OR(E14="",F14=""),"",IF((($E14="High")*3+($E14="Medium")*2+($E14="Low")*1)*(($F14="High")*3+($F14="Medium")*2+($F14="Low")*1)&gt;=6,"High",IF((($E14="High")*3+($E14="Medium")*2+($E14="Low")*1)*(($F14="High")*3+($F14="Medium")*2+($F14="Low")*1)&gt;=3,"Medium","Low")))</f>
         <v/>
       </c>
-      <c r="H14" s="7" t="n"/>
+      <c r="H14" s="10" t="n"/>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Narrow the API to Next-state endpoints; start once the KPI framework is agreed</t>
@@ -15253,7 +16420,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="24.85" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>R11</t>
@@ -15288,7 +16455,7 @@
         <f>IF(OR(E15="",F15=""),"",IF((($E15="High")*3+($E15="Medium")*2+($E15="Low")*1)*(($F15="High")*3+($F15="Medium")*2+($F15="Low")*1)&gt;=6,"High",IF((($E15="High")*3+($E15="Medium")*2+($E15="Low")*1)*(($F15="High")*3+($F15="Medium")*2+($F15="Low")*1)&gt;=3,"Medium","Low")))</f>
         <v/>
       </c>
-      <c r="H15" s="7" t="n"/>
+      <c r="H15" s="10" t="n"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>CLAUDE.md, this tracker, pairing</t>
@@ -15305,7 +16472,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="24.85" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>R12</t>
@@ -15452,7 +16619,7 @@
         <f>IF(OR(E18="",F18=""),"",IF((($E18="High")*3+($E18="Medium")*2+($E18="Low")*1)*(($F18="High")*3+($F18="Medium")*2+($F18="Low")*1)&gt;=6,"High",IF((($E18="High")*3+($E18="Medium")*2+($E18="Low")*1)*(($F18="High")*3+($F18="Medium")*2+($F18="Low")*1)&gt;=3,"Medium","Low")))</f>
         <v/>
       </c>
-      <c r="H18" s="7" t="n"/>
+      <c r="H18" s="10" t="n"/>
       <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Extend the test to all tabs</t>
@@ -15469,7 +16636,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="24.85" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>R15</t>
@@ -15504,7 +16671,7 @@
         <f>IF(OR(E19="",F19=""),"",IF((($E19="High")*3+($E19="Medium")*2+($E19="Low")*1)*(($F19="High")*3+($F19="Medium")*2+($F19="Low")*1)&gt;=6,"High",IF((($E19="High")*3+($E19="Medium")*2+($E19="Low")*1)*(($F19="High")*3+($F19="Medium")*2+($F19="Low")*1)&gt;=3,"Medium","Low")))</f>
         <v/>
       </c>
-      <c r="H19" s="7" t="n"/>
+      <c r="H19" s="10" t="n"/>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Re-price before quoting</t>
@@ -15521,7 +16688,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="24.85" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>R16</t>
@@ -15556,7 +16723,7 @@
         <f>IF(OR(E20="",F20=""),"",IF((($E20="High")*3+($E20="Medium")*2+($E20="Low")*1)*(($F20="High")*3+($F20="Medium")*2+($F20="Low")*1)&gt;=6,"High",IF((($E20="High")*3+($E20="Medium")*2+($E20="Low")*1)*(($F20="High")*3+($F20="Medium")*2+($F20="Low")*1)&gt;=3,"Medium","Low")))</f>
         <v/>
       </c>
-      <c r="H20" s="7" t="n"/>
+      <c r="H20" s="10" t="n"/>
       <c r="I20" s="5" t="inlineStr">
         <is>
           <t>Correct the documents; treat them as dated</t>
@@ -15608,7 +16775,7 @@
         <f>IF(OR(E21="",F21=""),"",IF((($E21="High")*3+($E21="Medium")*2+($E21="Low")*1)*(($F21="High")*3+($F21="Medium")*2+($F21="Low")*1)&gt;=6,"High",IF((($E21="High")*3+($E21="Medium")*2+($E21="Low")*1)*(($F21="High")*3+($F21="Medium")*2+($F21="Low")*1)&gt;=3,"Medium","Low")))</f>
         <v/>
       </c>
-      <c r="H21" s="7" t="n"/>
+      <c r="H21" s="10" t="n"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>Apply non-breaking npm audit fixes</t>
@@ -15625,7 +16792,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="24.85" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>R18</t>
@@ -15681,7 +16848,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="24.85" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>R19</t>
@@ -15716,7 +16883,7 @@
         <f>IF(OR(E23="",F23=""),"",IF((($E23="High")*3+($E23="Medium")*2+($E23="Low")*1)*(($F23="High")*3+($F23="Medium")*2+($F23="Low")*1)&gt;=6,"High",IF((($E23="High")*3+($E23="Medium")*2+($E23="Low")*1)*(($F23="High")*3+($F23="Medium")*2+($F23="Low")*1)&gt;=3,"Medium","Low")))</f>
         <v/>
       </c>
-      <c r="H23" s="7" t="n"/>
+      <c r="H23" s="10" t="n"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>Adopt this merged tracker (M8); retire the others</t>
@@ -15733,7 +16900,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="24.85" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>R20</t>
@@ -15768,7 +16935,7 @@
         <f>IF(OR(E24="",F24=""),"",IF((($E24="High")*3+($E24="Medium")*2+($E24="Low")*1)*(($F24="High")*3+($F24="Medium")*2+($F24="Low")*1)&gt;=6,"High",IF((($E24="High")*3+($E24="Medium")*2+($E24="Low")*1)*(($F24="High")*3+($F24="Medium")*2+($F24="Low")*1)&gt;=3,"Medium","Low")))</f>
         <v/>
       </c>
-      <c r="H24" s="7" t="n"/>
+      <c r="H24" s="10" t="n"/>
       <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Use Report 3 externally; verify sources; one rating scale</t>
@@ -15820,7 +16987,7 @@
         <f>IF(OR(E25="",F25=""),"",IF((($E25="High")*3+($E25="Medium")*2+($E25="Low")*1)*(($F25="High")*3+($F25="Medium")*2+($F25="Low")*1)&gt;=6,"High",IF((($E25="High")*3+($E25="Medium")*2+($E25="Low")*1)*(($F25="High")*3+($F25="Medium")*2+($F25="Low")*1)&gt;=3,"Medium","Low")))</f>
         <v/>
       </c>
-      <c r="H25" s="7" t="n"/>
+      <c r="H25" s="10" t="n"/>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>Estimate from the gap analyses in M8</t>
@@ -15837,7 +17004,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="62.15" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>R22</t>
@@ -15895,6 +17062,17 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:K26"/>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="2">
+      <formula>"High"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="4">
+      <formula>"Medium"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="5">
+      <formula>"Low"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"High"</formula>
@@ -15939,43 +17117,14 @@
       <formula>"Closed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G26">
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="2">
-      <formula>"High"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="4">
-      <formula>"Medium"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="5">
-      <formula>"Low"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="9">
-    <dataValidation sqref="B5:B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="B5:B25 B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Risk,Issue"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E25 E26 F5:F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"High,Medium,Low"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K5:K25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Open,Mitigated,Closed"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Risk,Issue"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"High,Medium,Low"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"High,Medium,Low"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Open,Mitigated,Closed"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K5:K25 K26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,Mitigated,Closed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15986,23 +17135,22 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00548235"/>
+    <tabColor rgb="FF548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.55"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="3" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.1" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Decisions — already made</t>
@@ -16017,43 +17165,43 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Alternatives considered</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Decided by</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Revisit if</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="24.85" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>D1</t>
@@ -16090,7 +17238,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="24.85" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>D2</t>
@@ -16127,7 +17275,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="24.85" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>D3</t>
@@ -16164,7 +17312,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="24.85" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>D4</t>
@@ -16275,7 +17423,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="24.85" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>D7</t>
@@ -16349,7 +17497,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="24.85" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>D9</t>
@@ -16460,7 +17608,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="24.85" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>D12</t>
@@ -16497,7 +17645,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="24.85" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>D13</t>
@@ -16534,7 +17682,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="24.85" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>D14</t>
